--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0003.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0003.xlsx
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Áp dụng</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Pioneer Association</t>
+          <t>Hiệp Hội Tiên Phong</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
     </row>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Làm mới</t>
         </is>
       </c>
     </row>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Lineup</t>
+          <t>Đội hình</t>
         </is>
       </c>
     </row>
@@ -17736,7 +17736,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18061,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -24301,7 +24301,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Bộ lọc</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Cửa hàng</t>
         </is>
       </c>
     </row>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Rewards Claimed Cấp Độ</t>
+          <t>Phần thưởng cấp độ đã nhận.</t>
         </is>
       </c>
     </row>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Claimed hết phần thưởng</t>
+          <t>Đã nhận hết phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -27486,7 +27486,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Cửa hàng</t>
         </is>
       </c>
     </row>
@@ -31581,7 +31581,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Send</t>
+          <t>Gửi</t>
         </is>
       </c>
     </row>
